--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13765" uniqueCount="849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13765" uniqueCount="850">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1089,6 +1089,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>SubstanceAdministration.statusCode</t>
@@ -14304,7 +14308,7 @@
         <v>74</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>74</v>
+        <v>348</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>74</v>
@@ -14312,10 +14316,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14341,10 +14345,10 @@
         <v>91</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14375,7 +14379,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>74</v>
@@ -14393,7 +14397,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -14413,10 +14417,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14514,10 +14518,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14558,7 +14562,7 @@
         <v>74</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>74</v>
@@ -14617,10 +14621,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14720,10 +14724,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14823,10 +14827,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14926,10 +14930,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15029,10 +15033,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15130,10 +15134,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15231,10 +15235,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15334,10 +15338,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15437,10 +15441,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15540,10 +15544,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15566,7 +15570,7 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -15607,7 +15611,7 @@
         <v>74</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AC123" s="2"/>
       <c r="AD123" t="s" s="2">
@@ -15617,7 +15621,7 @@
         <v>125</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -15637,13 +15641,13 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>74</v>
@@ -15665,10 +15669,10 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -15720,7 +15724,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -15732,7 +15736,7 @@
         <v>74</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>74</v>
@@ -15740,13 +15744,13 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>74</v>
@@ -15768,10 +15772,10 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -15823,7 +15827,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -15835,7 +15839,7 @@
         <v>74</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>74</v>
@@ -15843,10 +15847,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15869,7 +15873,7 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -15902,7 +15906,7 @@
       </c>
       <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>74</v>
@@ -15920,7 +15924,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -15940,10 +15944,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15966,7 +15970,7 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -16019,7 +16023,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -16039,10 +16043,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16065,13 +16069,13 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -16102,7 +16106,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>74</v>
@@ -16120,7 +16124,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -16140,10 +16144,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16169,10 +16173,10 @@
         <v>258</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -16203,7 +16207,7 @@
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>74</v>
@@ -16221,7 +16225,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -16241,10 +16245,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16342,10 +16346,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16445,10 +16449,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16548,10 +16552,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16651,10 +16655,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16754,10 +16758,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16857,10 +16861,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16958,10 +16962,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17059,10 +17063,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17162,10 +17166,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17263,10 +17267,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17364,10 +17368,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17467,10 +17471,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17568,10 +17572,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17671,10 +17675,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17772,10 +17776,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17869,10 +17873,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17974,10 +17978,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18077,10 +18081,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18172,7 +18176,7 @@
         <v>74</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>74</v>
+        <v>348</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>74</v>
@@ -18180,10 +18184,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18283,10 +18287,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18386,10 +18390,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18412,13 +18416,13 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -18469,7 +18473,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -18489,10 +18493,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18590,17 +18594,17 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F153" t="s" s="2">
         <v>80</v>
@@ -18622,7 +18626,7 @@
       </c>
       <c r="L153" s="2"/>
       <c r="M153" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -18673,7 +18677,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -18693,17 +18697,17 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F154" t="s" s="2">
         <v>80</v>
@@ -18721,11 +18725,11 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -18776,7 +18780,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -18796,10 +18800,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18824,11 +18828,11 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -18879,7 +18883,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -18899,10 +18903,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18929,12 +18933,12 @@
       </c>
       <c r="L156" s="2"/>
       <c r="M156" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q156" s="2"/>
       <c r="R156" t="s" s="2">
@@ -18960,7 +18964,7 @@
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>74</v>
@@ -18978,7 +18982,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -18998,17 +19002,17 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F157" t="s" s="2">
         <v>80</v>
@@ -19026,11 +19030,11 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -19081,7 +19085,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -19101,10 +19105,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19202,17 +19206,17 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F159" t="s" s="2">
         <v>80</v>
@@ -19234,7 +19238,7 @@
       </c>
       <c r="L159" s="2"/>
       <c r="M159" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -19285,7 +19289,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -19305,17 +19309,17 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E160" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F160" t="s" s="2">
         <v>80</v>
@@ -19333,11 +19337,11 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -19388,7 +19392,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -19408,10 +19412,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19436,11 +19440,11 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -19491,7 +19495,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -19511,10 +19515,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19612,10 +19616,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19715,10 +19719,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19818,10 +19822,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19921,10 +19925,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20024,10 +20028,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20127,10 +20131,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -20228,10 +20232,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20329,10 +20333,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20432,10 +20436,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20533,10 +20537,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20634,10 +20638,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20737,10 +20741,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20838,10 +20842,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20941,10 +20945,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -21042,10 +21046,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21139,10 +21143,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -21244,10 +21248,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21347,10 +21351,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -21442,7 +21446,7 @@
         <v>74</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>74</v>
+        <v>348</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>74</v>
@@ -21450,10 +21454,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21553,10 +21557,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -21656,10 +21660,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21684,11 +21688,11 @@
         <v>74</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -21739,7 +21743,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -21759,10 +21763,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21789,12 +21793,12 @@
       </c>
       <c r="L184" s="2"/>
       <c r="M184" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q184" s="2"/>
       <c r="R184" t="s" s="2">
@@ -21840,7 +21844,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -21860,17 +21864,17 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E185" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F185" t="s" s="2">
         <v>80</v>
@@ -21888,11 +21892,11 @@
         <v>74</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L185" s="2"/>
       <c r="M185" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -21943,7 +21947,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -21963,17 +21967,17 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E186" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F186" t="s" s="2">
         <v>80</v>
@@ -21991,11 +21995,11 @@
         <v>74</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -22046,7 +22050,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -22066,17 +22070,17 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F187" t="s" s="2">
         <v>80</v>
@@ -22094,11 +22098,11 @@
         <v>74</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -22149,7 +22153,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -22169,10 +22173,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -22270,17 +22274,17 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E189" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F189" t="s" s="2">
         <v>80</v>
@@ -22302,7 +22306,7 @@
       </c>
       <c r="L189" s="2"/>
       <c r="M189" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -22353,7 +22357,7 @@
         <v>74</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -22373,17 +22377,17 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E190" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F190" t="s" s="2">
         <v>80</v>
@@ -22401,11 +22405,11 @@
         <v>74</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -22456,7 +22460,7 @@
         <v>74</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -22476,10 +22480,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -22504,11 +22508,11 @@
         <v>74</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -22559,7 +22563,7 @@
         <v>74</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -22579,10 +22583,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -22680,10 +22684,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -22783,10 +22787,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22886,10 +22890,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22989,10 +22993,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -23092,10 +23096,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -23195,10 +23199,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -23296,10 +23300,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -23397,10 +23401,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -23500,10 +23504,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -23601,10 +23605,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -23702,10 +23706,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -23805,10 +23809,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -23906,10 +23910,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -24009,10 +24013,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -24110,10 +24114,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -24207,10 +24211,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -24312,10 +24316,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -24415,10 +24419,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -24510,7 +24514,7 @@
         <v>74</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>74</v>
+        <v>348</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>74</v>
@@ -24518,10 +24522,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -24621,10 +24625,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -24724,10 +24728,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -24752,11 +24756,11 @@
         <v>74</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L213" s="2"/>
       <c r="M213" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -24807,7 +24811,7 @@
         <v>74</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -24827,10 +24831,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24857,12 +24861,12 @@
       </c>
       <c r="L214" s="2"/>
       <c r="M214" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q214" s="2"/>
       <c r="R214" t="s" s="2">
@@ -24908,7 +24912,7 @@
         <v>74</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -24928,10 +24932,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -24954,10 +24958,10 @@
         <v>74</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M215" s="2"/>
       <c r="N215" s="2"/>
@@ -25009,7 +25013,7 @@
         <v>74</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -25029,10 +25033,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -25130,17 +25134,17 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E217" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F217" t="s" s="2">
         <v>80</v>
@@ -25162,7 +25166,7 @@
       </c>
       <c r="L217" s="2"/>
       <c r="M217" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -25213,7 +25217,7 @@
         <v>74</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
@@ -25233,17 +25237,17 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E218" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F218" t="s" s="2">
         <v>80</v>
@@ -25261,11 +25265,11 @@
         <v>74</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L218" s="2"/>
       <c r="M218" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -25316,7 +25320,7 @@
         <v>74</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>80</v>
@@ -25336,10 +25340,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -25364,11 +25368,11 @@
         <v>74</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -25419,7 +25423,7 @@
         <v>74</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
@@ -25439,10 +25443,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -25469,12 +25473,12 @@
       </c>
       <c r="L220" s="2"/>
       <c r="M220" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q220" s="2"/>
       <c r="R220" t="s" s="2">
@@ -25500,7 +25504,7 @@
       </c>
       <c r="Y220" s="2"/>
       <c r="Z220" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>74</v>
@@ -25518,7 +25522,7 @@
         <v>74</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
@@ -25538,17 +25542,17 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E221" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F221" t="s" s="2">
         <v>75</v>
@@ -25566,11 +25570,11 @@
         <v>74</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
@@ -25621,7 +25625,7 @@
         <v>74</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
@@ -25641,10 +25645,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -25742,17 +25746,17 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E223" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F223" t="s" s="2">
         <v>80</v>
@@ -25774,7 +25778,7 @@
       </c>
       <c r="L223" s="2"/>
       <c r="M223" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -25825,7 +25829,7 @@
         <v>74</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -25845,17 +25849,17 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E224" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F224" t="s" s="2">
         <v>80</v>
@@ -25873,11 +25877,11 @@
         <v>74</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -25928,7 +25932,7 @@
         <v>74</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -25948,10 +25952,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25976,11 +25980,11 @@
         <v>74</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L225" s="2"/>
       <c r="M225" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -26031,7 +26035,7 @@
         <v>74</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -26051,10 +26055,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -26152,10 +26156,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -26255,10 +26259,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -26358,10 +26362,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -26461,10 +26465,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -26564,10 +26568,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -26667,10 +26671,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -26768,10 +26772,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -26869,10 +26873,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -26972,10 +26976,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -27073,10 +27077,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -27174,10 +27178,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -27277,10 +27281,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -27378,10 +27382,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -27481,10 +27485,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -27582,10 +27586,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -27679,10 +27683,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -27784,10 +27788,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -27887,10 +27891,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -27982,7 +27986,7 @@
         <v>74</v>
       </c>
       <c r="AJ244" t="s" s="2">
-        <v>74</v>
+        <v>348</v>
       </c>
       <c r="AK244" t="s" s="2">
         <v>74</v>
@@ -27990,10 +27994,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -28093,10 +28097,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -28196,10 +28200,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -28224,11 +28228,11 @@
         <v>74</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L247" s="2"/>
       <c r="M247" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" s="2"/>
@@ -28279,7 +28283,7 @@
         <v>74</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>80</v>
@@ -28299,10 +28303,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -28329,12 +28333,12 @@
       </c>
       <c r="L248" s="2"/>
       <c r="M248" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" s="2"/>
       <c r="P248" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q248" s="2"/>
       <c r="R248" t="s" s="2">
@@ -28380,7 +28384,7 @@
         <v>74</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>80</v>
@@ -28400,17 +28404,17 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E249" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F249" t="s" s="2">
         <v>80</v>
@@ -28428,11 +28432,11 @@
         <v>74</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L249" s="2"/>
       <c r="M249" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" s="2"/>
@@ -28483,7 +28487,7 @@
         <v>74</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>80</v>
@@ -28503,17 +28507,17 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E250" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F250" t="s" s="2">
         <v>80</v>
@@ -28531,11 +28535,11 @@
         <v>74</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L250" s="2"/>
       <c r="M250" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" s="2"/>
@@ -28586,7 +28590,7 @@
         <v>74</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>80</v>
@@ -28606,17 +28610,17 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E251" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F251" t="s" s="2">
         <v>75</v>
@@ -28634,11 +28638,11 @@
         <v>74</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L251" s="2"/>
       <c r="M251" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -28689,7 +28693,7 @@
         <v>74</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>80</v>
@@ -28709,10 +28713,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -28810,17 +28814,17 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E253" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F253" t="s" s="2">
         <v>80</v>
@@ -28842,7 +28846,7 @@
       </c>
       <c r="L253" s="2"/>
       <c r="M253" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
@@ -28893,7 +28897,7 @@
         <v>74</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>80</v>
@@ -28913,17 +28917,17 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E254" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F254" t="s" s="2">
         <v>80</v>
@@ -28941,11 +28945,11 @@
         <v>74</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L254" s="2"/>
       <c r="M254" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
@@ -28996,7 +29000,7 @@
         <v>74</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>80</v>
@@ -29016,10 +29020,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -29044,11 +29048,11 @@
         <v>74</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L255" s="2"/>
       <c r="M255" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N255" s="2"/>
       <c r="O255" s="2"/>
@@ -29099,7 +29103,7 @@
         <v>74</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>80</v>
@@ -29119,10 +29123,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -29220,10 +29224,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -29323,10 +29327,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -29426,10 +29430,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -29529,10 +29533,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -29632,10 +29636,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -29735,10 +29739,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -29836,10 +29840,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -29937,10 +29941,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -30040,10 +30044,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -30141,10 +30145,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -30242,10 +30246,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -30345,10 +30349,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -30446,10 +30450,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -30549,10 +30553,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -30650,10 +30654,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -30747,10 +30751,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -30852,10 +30856,10 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -30955,10 +30959,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -31050,7 +31054,7 @@
         <v>74</v>
       </c>
       <c r="AJ274" t="s" s="2">
-        <v>74</v>
+        <v>348</v>
       </c>
       <c r="AK274" t="s" s="2">
         <v>74</v>
@@ -31058,10 +31062,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -31161,10 +31165,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -31264,10 +31268,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -31292,11 +31296,11 @@
         <v>74</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L277" s="2"/>
       <c r="M277" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N277" s="2"/>
       <c r="O277" s="2"/>
@@ -31347,7 +31351,7 @@
         <v>74</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>80</v>
@@ -31367,10 +31371,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -31397,12 +31401,12 @@
       </c>
       <c r="L278" s="2"/>
       <c r="M278" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N278" s="2"/>
       <c r="O278" s="2"/>
       <c r="P278" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q278" s="2"/>
       <c r="R278" t="s" s="2">
@@ -31448,7 +31452,7 @@
         <v>74</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>80</v>
@@ -31468,10 +31472,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -31494,10 +31498,10 @@
         <v>74</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M279" s="2"/>
       <c r="N279" s="2"/>
@@ -31549,7 +31553,7 @@
         <v>74</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>80</v>
@@ -31569,10 +31573,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -31670,17 +31674,17 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E281" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F281" t="s" s="2">
         <v>75</v>
@@ -31698,11 +31702,11 @@
         <v>74</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L281" s="2"/>
       <c r="M281" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
@@ -31753,7 +31757,7 @@
         <v>74</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>80</v>
@@ -31773,10 +31777,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -31874,17 +31878,17 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E283" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F283" t="s" s="2">
         <v>80</v>
@@ -31906,7 +31910,7 @@
       </c>
       <c r="L283" s="2"/>
       <c r="M283" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" s="2"/>
@@ -31957,7 +31961,7 @@
         <v>74</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>80</v>
@@ -31977,17 +31981,17 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E284" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F284" t="s" s="2">
         <v>80</v>
@@ -32005,11 +32009,11 @@
         <v>74</v>
       </c>
       <c r="K284" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L284" s="2"/>
       <c r="M284" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" s="2"/>
@@ -32060,7 +32064,7 @@
         <v>74</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>80</v>
@@ -32080,10 +32084,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -32108,11 +32112,11 @@
         <v>74</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L285" s="2"/>
       <c r="M285" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N285" s="2"/>
       <c r="O285" s="2"/>
@@ -32163,7 +32167,7 @@
         <v>74</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>80</v>
@@ -32183,17 +32187,17 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E286" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F286" t="s" s="2">
         <v>75</v>
@@ -32211,11 +32215,11 @@
         <v>74</v>
       </c>
       <c r="K286" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L286" s="2"/>
       <c r="M286" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" s="2"/>
@@ -32266,7 +32270,7 @@
         <v>74</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>80</v>
@@ -32286,10 +32290,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -32387,17 +32391,17 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E288" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F288" t="s" s="2">
         <v>80</v>
@@ -32419,7 +32423,7 @@
       </c>
       <c r="L288" s="2"/>
       <c r="M288" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N288" s="2"/>
       <c r="O288" s="2"/>
@@ -32470,7 +32474,7 @@
         <v>74</v>
       </c>
       <c r="AF288" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG288" t="s" s="2">
         <v>80</v>
@@ -32490,17 +32494,17 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E289" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F289" t="s" s="2">
         <v>80</v>
@@ -32518,11 +32522,11 @@
         <v>74</v>
       </c>
       <c r="K289" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L289" s="2"/>
       <c r="M289" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="2"/>
@@ -32573,7 +32577,7 @@
         <v>74</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>80</v>
@@ -32593,10 +32597,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -32621,11 +32625,11 @@
         <v>74</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L290" s="2"/>
       <c r="M290" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N290" s="2"/>
       <c r="O290" s="2"/>
@@ -32676,7 +32680,7 @@
         <v>74</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>80</v>
@@ -32696,10 +32700,10 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -32722,7 +32726,7 @@
         <v>74</v>
       </c>
       <c r="K291" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L291" s="2"/>
       <c r="M291" s="2"/>
@@ -32755,25 +32759,25 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AA291" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB291" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC291" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD291" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE291" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF291" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="AA291" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB291" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC291" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD291" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE291" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF291" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="AG291" t="s" s="2">
         <v>80</v>
@@ -32793,10 +32797,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -32819,13 +32823,13 @@
         <v>74</v>
       </c>
       <c r="K292" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N292" s="2"/>
       <c r="O292" s="2"/>
@@ -32876,7 +32880,7 @@
         <v>74</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG292" t="s" s="2">
         <v>75</v>
@@ -32896,10 +32900,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -32997,10 +33001,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -33098,10 +33102,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -33199,10 +33203,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -33300,10 +33304,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -33403,10 +33407,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -33506,10 +33510,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -33609,10 +33613,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -33712,10 +33716,10 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
@@ -33813,10 +33817,10 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" t="s" s="2">
@@ -33850,7 +33854,7 @@
       </c>
       <c r="Q302" s="2"/>
       <c r="R302" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="S302" t="s" s="2">
         <v>74</v>
@@ -33872,7 +33876,7 @@
       </c>
       <c r="Y302" s="2"/>
       <c r="Z302" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AA302" t="s" s="2">
         <v>74</v>
@@ -33890,7 +33894,7 @@
         <v>74</v>
       </c>
       <c r="AF302" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG302" t="s" s="2">
         <v>80</v>
@@ -33910,10 +33914,10 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -33936,7 +33940,7 @@
         <v>74</v>
       </c>
       <c r="K303" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L303" s="2"/>
       <c r="M303" s="2"/>
@@ -33989,7 +33993,7 @@
         <v>74</v>
       </c>
       <c r="AF303" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG303" t="s" s="2">
         <v>75</v>
@@ -34009,10 +34013,10 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
@@ -34035,7 +34039,7 @@
         <v>74</v>
       </c>
       <c r="K304" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L304" s="2"/>
       <c r="M304" s="2"/>
@@ -34088,7 +34092,7 @@
         <v>74</v>
       </c>
       <c r="AF304" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG304" t="s" s="2">
         <v>80</v>
@@ -34108,10 +34112,10 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
@@ -34134,7 +34138,7 @@
         <v>74</v>
       </c>
       <c r="K305" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L305" s="2"/>
       <c r="M305" s="2"/>
@@ -34187,7 +34191,7 @@
         <v>74</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>80</v>
@@ -34207,10 +34211,10 @@
     </row>
     <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" t="s" s="2">
@@ -34233,7 +34237,7 @@
         <v>74</v>
       </c>
       <c r="K306" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L306" s="2"/>
       <c r="M306" s="2"/>
@@ -34286,7 +34290,7 @@
         <v>74</v>
       </c>
       <c r="AF306" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG306" t="s" s="2">
         <v>80</v>
@@ -34306,10 +34310,10 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" t="s" s="2">
@@ -34332,7 +34336,7 @@
         <v>74</v>
       </c>
       <c r="K307" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L307" s="2"/>
       <c r="M307" s="2"/>
@@ -34385,7 +34389,7 @@
         <v>74</v>
       </c>
       <c r="AF307" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG307" t="s" s="2">
         <v>80</v>
@@ -34405,10 +34409,10 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" t="s" s="2">
@@ -34431,7 +34435,7 @@
         <v>74</v>
       </c>
       <c r="K308" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L308" s="2"/>
       <c r="M308" s="2"/>
@@ -34484,7 +34488,7 @@
         <v>74</v>
       </c>
       <c r="AF308" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG308" t="s" s="2">
         <v>80</v>
@@ -34504,10 +34508,10 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" t="s" s="2">
@@ -34530,7 +34534,7 @@
         <v>74</v>
       </c>
       <c r="K309" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L309" s="2"/>
       <c r="M309" s="2"/>
@@ -34583,7 +34587,7 @@
         <v>74</v>
       </c>
       <c r="AF309" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG309" t="s" s="2">
         <v>80</v>
@@ -34603,10 +34607,10 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" t="s" s="2">
@@ -34629,7 +34633,7 @@
         <v>74</v>
       </c>
       <c r="K310" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L310" s="2"/>
       <c r="M310" s="2"/>
@@ -34670,7 +34674,7 @@
         <v>74</v>
       </c>
       <c r="AB310" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AC310" s="2"/>
       <c r="AD310" t="s" s="2">
@@ -34680,7 +34684,7 @@
         <v>125</v>
       </c>
       <c r="AF310" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG310" t="s" s="2">
         <v>80</v>
@@ -34700,13 +34704,13 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D311" t="s" s="2">
         <v>74</v>
@@ -34728,13 +34732,13 @@
         <v>74</v>
       </c>
       <c r="K311" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N311" s="2"/>
       <c r="O311" s="2"/>
@@ -34785,7 +34789,7 @@
         <v>74</v>
       </c>
       <c r="AF311" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG311" t="s" s="2">
         <v>80</v>
@@ -34805,10 +34809,10 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" t="s" s="2">
@@ -34906,10 +34910,10 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" t="s" s="2">
@@ -35007,10 +35011,10 @@
     </row>
     <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" t="s" s="2">
@@ -35108,10 +35112,10 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" t="s" s="2">
@@ -35209,10 +35213,10 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" t="s" s="2">
@@ -35312,10 +35316,10 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" t="s" s="2">
@@ -35415,10 +35419,10 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" t="s" s="2">
@@ -35518,10 +35522,10 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" t="s" s="2">
@@ -35621,10 +35625,10 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" t="s" s="2">
@@ -35722,10 +35726,10 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" t="s" s="2">
@@ -35762,7 +35766,7 @@
         <v>74</v>
       </c>
       <c r="S321" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="T321" t="s" s="2">
         <v>74</v>
@@ -35781,7 +35785,7 @@
       </c>
       <c r="Y321" s="2"/>
       <c r="Z321" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AA321" t="s" s="2">
         <v>74</v>
@@ -35799,7 +35803,7 @@
         <v>74</v>
       </c>
       <c r="AF321" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG321" t="s" s="2">
         <v>75</v>
@@ -35819,10 +35823,10 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" t="s" s="2">
@@ -35849,7 +35853,7 @@
       </c>
       <c r="L322" s="2"/>
       <c r="M322" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N322" s="2"/>
       <c r="O322" s="2"/>
@@ -35900,7 +35904,7 @@
         <v>74</v>
       </c>
       <c r="AF322" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG322" t="s" s="2">
         <v>80</v>
@@ -35920,10 +35924,10 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" t="s" s="2">
@@ -35950,12 +35954,12 @@
       </c>
       <c r="L323" s="2"/>
       <c r="M323" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N323" s="2"/>
       <c r="O323" s="2"/>
       <c r="P323" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q323" s="2"/>
       <c r="R323" t="s" s="2">
@@ -36001,7 +36005,7 @@
         <v>74</v>
       </c>
       <c r="AF323" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG323" t="s" s="2">
         <v>80</v>
@@ -36021,10 +36025,10 @@
     </row>
     <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" t="s" s="2">
@@ -36100,7 +36104,7 @@
         <v>74</v>
       </c>
       <c r="AF324" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG324" t="s" s="2">
         <v>80</v>
@@ -36120,10 +36124,10 @@
     </row>
     <row r="325" hidden="true">
       <c r="A325" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" t="s" s="2">
@@ -36146,7 +36150,7 @@
         <v>74</v>
       </c>
       <c r="K325" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L325" s="2"/>
       <c r="M325" s="2"/>
@@ -36199,7 +36203,7 @@
         <v>74</v>
       </c>
       <c r="AF325" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG325" t="s" s="2">
         <v>80</v>
@@ -36219,10 +36223,10 @@
     </row>
     <row r="326" hidden="true">
       <c r="A326" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" t="s" s="2">
@@ -36245,7 +36249,7 @@
         <v>74</v>
       </c>
       <c r="K326" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L326" s="2"/>
       <c r="M326" s="2"/>
@@ -36298,7 +36302,7 @@
         <v>74</v>
       </c>
       <c r="AF326" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG326" t="s" s="2">
         <v>80</v>
@@ -36318,10 +36322,10 @@
     </row>
     <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" t="s" s="2">
@@ -36344,7 +36348,7 @@
         <v>74</v>
       </c>
       <c r="K327" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L327" s="2"/>
       <c r="M327" s="2"/>
@@ -36397,7 +36401,7 @@
         <v>74</v>
       </c>
       <c r="AF327" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG327" t="s" s="2">
         <v>80</v>
@@ -36417,10 +36421,10 @@
     </row>
     <row r="328" hidden="true">
       <c r="A328" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" t="s" s="2">
@@ -36443,7 +36447,7 @@
         <v>74</v>
       </c>
       <c r="K328" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L328" s="2"/>
       <c r="M328" s="2"/>
@@ -36496,7 +36500,7 @@
         <v>74</v>
       </c>
       <c r="AF328" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG328" t="s" s="2">
         <v>80</v>
@@ -36516,10 +36520,10 @@
     </row>
     <row r="329" hidden="true">
       <c r="A329" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C329" s="2"/>
       <c r="D329" t="s" s="2">
@@ -36542,7 +36546,7 @@
         <v>74</v>
       </c>
       <c r="K329" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L329" s="2"/>
       <c r="M329" s="2"/>
@@ -36595,7 +36599,7 @@
         <v>74</v>
       </c>
       <c r="AF329" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG329" t="s" s="2">
         <v>80</v>
@@ -36615,10 +36619,10 @@
     </row>
     <row r="330" hidden="true">
       <c r="A330" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" t="s" s="2">
@@ -36641,7 +36645,7 @@
         <v>74</v>
       </c>
       <c r="K330" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L330" s="2"/>
       <c r="M330" s="2"/>
@@ -36694,7 +36698,7 @@
         <v>74</v>
       </c>
       <c r="AF330" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG330" t="s" s="2">
         <v>80</v>
@@ -36714,10 +36718,10 @@
     </row>
     <row r="331" hidden="true">
       <c r="A331" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" t="s" s="2">
@@ -36740,7 +36744,7 @@
         <v>74</v>
       </c>
       <c r="K331" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L331" s="2"/>
       <c r="M331" s="2"/>
@@ -36793,7 +36797,7 @@
         <v>74</v>
       </c>
       <c r="AF331" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG331" t="s" s="2">
         <v>80</v>
@@ -36813,10 +36817,10 @@
     </row>
     <row r="332" hidden="true">
       <c r="A332" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" t="s" s="2">
@@ -36839,7 +36843,7 @@
         <v>74</v>
       </c>
       <c r="K332" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L332" s="2"/>
       <c r="M332" s="2"/>
@@ -36892,7 +36896,7 @@
         <v>74</v>
       </c>
       <c r="AF332" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG332" t="s" s="2">
         <v>80</v>
@@ -36912,10 +36916,10 @@
     </row>
     <row r="333" hidden="true">
       <c r="A333" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" t="s" s="2">
@@ -36938,7 +36942,7 @@
         <v>74</v>
       </c>
       <c r="K333" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L333" s="2"/>
       <c r="M333" s="2"/>
@@ -36991,7 +36995,7 @@
         <v>74</v>
       </c>
       <c r="AF333" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG333" t="s" s="2">
         <v>80</v>
@@ -37011,10 +37015,10 @@
     </row>
     <row r="334" hidden="true">
       <c r="A334" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C334" s="2"/>
       <c r="D334" t="s" s="2">
@@ -37037,7 +37041,7 @@
         <v>74</v>
       </c>
       <c r="K334" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L334" s="2"/>
       <c r="M334" s="2"/>
@@ -37090,7 +37094,7 @@
         <v>74</v>
       </c>
       <c r="AF334" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG334" t="s" s="2">
         <v>80</v>
@@ -37110,10 +37114,10 @@
     </row>
     <row r="335" hidden="true">
       <c r="A335" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" t="s" s="2">
@@ -37136,7 +37140,7 @@
         <v>74</v>
       </c>
       <c r="K335" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L335" s="2"/>
       <c r="M335" s="2"/>
@@ -37189,7 +37193,7 @@
         <v>74</v>
       </c>
       <c r="AF335" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG335" t="s" s="2">
         <v>80</v>
@@ -37209,13 +37213,13 @@
     </row>
     <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D336" t="s" s="2">
         <v>74</v>
@@ -37237,7 +37241,7 @@
         <v>74</v>
       </c>
       <c r="K336" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L336" s="2"/>
       <c r="M336" s="2"/>
@@ -37290,7 +37294,7 @@
         <v>74</v>
       </c>
       <c r="AF336" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG336" t="s" s="2">
         <v>80</v>
@@ -37310,10 +37314,10 @@
     </row>
     <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" t="s" s="2">
@@ -37411,10 +37415,10 @@
     </row>
     <row r="338" hidden="true">
       <c r="A338" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" t="s" s="2">
@@ -37512,10 +37516,10 @@
     </row>
     <row r="339" hidden="true">
       <c r="A339" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" t="s" s="2">
@@ -37613,10 +37617,10 @@
     </row>
     <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" t="s" s="2">
@@ -37714,10 +37718,10 @@
     </row>
     <row r="341" hidden="true">
       <c r="A341" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" t="s" s="2">
@@ -37817,10 +37821,10 @@
     </row>
     <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" t="s" s="2">
@@ -37920,10 +37924,10 @@
     </row>
     <row r="343" hidden="true">
       <c r="A343" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" t="s" s="2">
@@ -38023,10 +38027,10 @@
     </row>
     <row r="344" hidden="true">
       <c r="A344" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C344" s="2"/>
       <c r="D344" t="s" s="2">
@@ -38126,10 +38130,10 @@
     </row>
     <row r="345" hidden="true">
       <c r="A345" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" t="s" s="2">
@@ -38227,10 +38231,10 @@
     </row>
     <row r="346" hidden="true">
       <c r="A346" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C346" s="2"/>
       <c r="D346" t="s" s="2">
@@ -38267,7 +38271,7 @@
         <v>74</v>
       </c>
       <c r="S346" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="T346" t="s" s="2">
         <v>74</v>
@@ -38286,7 +38290,7 @@
       </c>
       <c r="Y346" s="2"/>
       <c r="Z346" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AA346" t="s" s="2">
         <v>74</v>
@@ -38304,7 +38308,7 @@
         <v>74</v>
       </c>
       <c r="AF346" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG346" t="s" s="2">
         <v>75</v>
@@ -38324,10 +38328,10 @@
     </row>
     <row r="347" hidden="true">
       <c r="A347" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C347" s="2"/>
       <c r="D347" t="s" s="2">
@@ -38354,7 +38358,7 @@
       </c>
       <c r="L347" s="2"/>
       <c r="M347" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N347" s="2"/>
       <c r="O347" s="2"/>
@@ -38405,7 +38409,7 @@
         <v>74</v>
       </c>
       <c r="AF347" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG347" t="s" s="2">
         <v>80</v>
@@ -38425,10 +38429,10 @@
     </row>
     <row r="348" hidden="true">
       <c r="A348" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C348" s="2"/>
       <c r="D348" t="s" s="2">
@@ -38455,12 +38459,12 @@
       </c>
       <c r="L348" s="2"/>
       <c r="M348" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N348" s="2"/>
       <c r="O348" s="2"/>
       <c r="P348" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q348" s="2"/>
       <c r="R348" t="s" s="2">
@@ -38506,7 +38510,7 @@
         <v>74</v>
       </c>
       <c r="AF348" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG348" t="s" s="2">
         <v>80</v>
@@ -38526,10 +38530,10 @@
     </row>
     <row r="349" hidden="true">
       <c r="A349" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C349" s="2"/>
       <c r="D349" t="s" s="2">
@@ -38605,7 +38609,7 @@
         <v>74</v>
       </c>
       <c r="AF349" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG349" t="s" s="2">
         <v>80</v>
@@ -38625,10 +38629,10 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" t="s" s="2">
@@ -38651,7 +38655,7 @@
         <v>74</v>
       </c>
       <c r="K350" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L350" s="2"/>
       <c r="M350" s="2"/>
@@ -38704,7 +38708,7 @@
         <v>74</v>
       </c>
       <c r="AF350" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG350" t="s" s="2">
         <v>80</v>
@@ -38724,10 +38728,10 @@
     </row>
     <row r="351" hidden="true">
       <c r="A351" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C351" s="2"/>
       <c r="D351" t="s" s="2">
@@ -38750,7 +38754,7 @@
         <v>74</v>
       </c>
       <c r="K351" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L351" s="2"/>
       <c r="M351" s="2"/>
@@ -38803,7 +38807,7 @@
         <v>74</v>
       </c>
       <c r="AF351" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG351" t="s" s="2">
         <v>80</v>
@@ -38823,10 +38827,10 @@
     </row>
     <row r="352" hidden="true">
       <c r="A352" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C352" s="2"/>
       <c r="D352" t="s" s="2">
@@ -38849,7 +38853,7 @@
         <v>74</v>
       </c>
       <c r="K352" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L352" s="2"/>
       <c r="M352" s="2"/>
@@ -38902,7 +38906,7 @@
         <v>74</v>
       </c>
       <c r="AF352" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG352" t="s" s="2">
         <v>80</v>
@@ -38922,10 +38926,10 @@
     </row>
     <row r="353" hidden="true">
       <c r="A353" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C353" s="2"/>
       <c r="D353" t="s" s="2">
@@ -38948,7 +38952,7 @@
         <v>74</v>
       </c>
       <c r="K353" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L353" s="2"/>
       <c r="M353" s="2"/>
@@ -39001,7 +39005,7 @@
         <v>74</v>
       </c>
       <c r="AF353" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG353" t="s" s="2">
         <v>80</v>
@@ -39021,10 +39025,10 @@
     </row>
     <row r="354" hidden="true">
       <c r="A354" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C354" s="2"/>
       <c r="D354" t="s" s="2">
@@ -39047,7 +39051,7 @@
         <v>74</v>
       </c>
       <c r="K354" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L354" s="2"/>
       <c r="M354" s="2"/>
@@ -39100,7 +39104,7 @@
         <v>74</v>
       </c>
       <c r="AF354" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG354" t="s" s="2">
         <v>80</v>
@@ -39120,10 +39124,10 @@
     </row>
     <row r="355" hidden="true">
       <c r="A355" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C355" s="2"/>
       <c r="D355" t="s" s="2">
@@ -39146,7 +39150,7 @@
         <v>74</v>
       </c>
       <c r="K355" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L355" s="2"/>
       <c r="M355" s="2"/>
@@ -39199,7 +39203,7 @@
         <v>74</v>
       </c>
       <c r="AF355" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG355" t="s" s="2">
         <v>80</v>
@@ -39219,10 +39223,10 @@
     </row>
     <row r="356" hidden="true">
       <c r="A356" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C356" s="2"/>
       <c r="D356" t="s" s="2">
@@ -39245,7 +39249,7 @@
         <v>74</v>
       </c>
       <c r="K356" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L356" s="2"/>
       <c r="M356" s="2"/>
@@ -39298,7 +39302,7 @@
         <v>74</v>
       </c>
       <c r="AF356" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG356" t="s" s="2">
         <v>80</v>
@@ -39318,10 +39322,10 @@
     </row>
     <row r="357" hidden="true">
       <c r="A357" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C357" s="2"/>
       <c r="D357" t="s" s="2">
@@ -39344,7 +39348,7 @@
         <v>74</v>
       </c>
       <c r="K357" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L357" s="2"/>
       <c r="M357" s="2"/>
@@ -39397,7 +39401,7 @@
         <v>74</v>
       </c>
       <c r="AF357" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG357" t="s" s="2">
         <v>80</v>
@@ -39417,10 +39421,10 @@
     </row>
     <row r="358" hidden="true">
       <c r="A358" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C358" s="2"/>
       <c r="D358" t="s" s="2">
@@ -39443,7 +39447,7 @@
         <v>74</v>
       </c>
       <c r="K358" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L358" s="2"/>
       <c r="M358" s="2"/>
@@ -39496,7 +39500,7 @@
         <v>74</v>
       </c>
       <c r="AF358" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG358" t="s" s="2">
         <v>80</v>
@@ -39516,10 +39520,10 @@
     </row>
     <row r="359" hidden="true">
       <c r="A359" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C359" s="2"/>
       <c r="D359" t="s" s="2">
@@ -39542,13 +39546,13 @@
         <v>74</v>
       </c>
       <c r="K359" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L359" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M359" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N359" s="2"/>
       <c r="O359" s="2"/>
@@ -39599,7 +39603,7 @@
         <v>74</v>
       </c>
       <c r="AF359" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG359" t="s" s="2">
         <v>80</v>
@@ -39619,10 +39623,10 @@
     </row>
     <row r="360" hidden="true">
       <c r="A360" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C360" s="2"/>
       <c r="D360" t="s" s="2">
@@ -39645,7 +39649,7 @@
         <v>74</v>
       </c>
       <c r="K360" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="L360" s="2"/>
       <c r="M360" s="2"/>
@@ -39698,7 +39702,7 @@
         <v>74</v>
       </c>
       <c r="AF360" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG360" t="s" s="2">
         <v>80</v>
@@ -39718,13 +39722,13 @@
     </row>
     <row r="361" hidden="true">
       <c r="A361" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D361" t="s" s="2">
         <v>74</v>
@@ -39746,7 +39750,7 @@
         <v>74</v>
       </c>
       <c r="K361" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L361" s="2"/>
       <c r="M361" s="2"/>
@@ -39799,7 +39803,7 @@
         <v>74</v>
       </c>
       <c r="AF361" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG361" t="s" s="2">
         <v>80</v>
@@ -39819,10 +39823,10 @@
     </row>
     <row r="362" hidden="true">
       <c r="A362" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C362" s="2"/>
       <c r="D362" t="s" s="2">
@@ -39920,10 +39924,10 @@
     </row>
     <row r="363" hidden="true">
       <c r="A363" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C363" s="2"/>
       <c r="D363" t="s" s="2">
@@ -40021,10 +40025,10 @@
     </row>
     <row r="364" hidden="true">
       <c r="A364" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C364" s="2"/>
       <c r="D364" t="s" s="2">
@@ -40122,10 +40126,10 @@
     </row>
     <row r="365" hidden="true">
       <c r="A365" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C365" s="2"/>
       <c r="D365" t="s" s="2">
@@ -40223,10 +40227,10 @@
     </row>
     <row r="366" hidden="true">
       <c r="A366" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C366" s="2"/>
       <c r="D366" t="s" s="2">
@@ -40326,10 +40330,10 @@
     </row>
     <row r="367" hidden="true">
       <c r="A367" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C367" s="2"/>
       <c r="D367" t="s" s="2">
@@ -40429,10 +40433,10 @@
     </row>
     <row r="368" hidden="true">
       <c r="A368" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C368" s="2"/>
       <c r="D368" t="s" s="2">
@@ -40532,10 +40536,10 @@
     </row>
     <row r="369" hidden="true">
       <c r="A369" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C369" s="2"/>
       <c r="D369" t="s" s="2">
@@ -40635,10 +40639,10 @@
     </row>
     <row r="370" hidden="true">
       <c r="A370" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C370" s="2"/>
       <c r="D370" t="s" s="2">
@@ -40736,10 +40740,10 @@
     </row>
     <row r="371" hidden="true">
       <c r="A371" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C371" s="2"/>
       <c r="D371" t="s" s="2">
@@ -40776,7 +40780,7 @@
         <v>74</v>
       </c>
       <c r="S371" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="T371" t="s" s="2">
         <v>74</v>
@@ -40795,7 +40799,7 @@
       </c>
       <c r="Y371" s="2"/>
       <c r="Z371" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AA371" t="s" s="2">
         <v>74</v>
@@ -40813,7 +40817,7 @@
         <v>74</v>
       </c>
       <c r="AF371" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG371" t="s" s="2">
         <v>75</v>
@@ -40833,10 +40837,10 @@
     </row>
     <row r="372" hidden="true">
       <c r="A372" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C372" s="2"/>
       <c r="D372" t="s" s="2">
@@ -40863,7 +40867,7 @@
       </c>
       <c r="L372" s="2"/>
       <c r="M372" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N372" s="2"/>
       <c r="O372" s="2"/>
@@ -40875,7 +40879,7 @@
         <v>74</v>
       </c>
       <c r="S372" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="T372" t="s" s="2">
         <v>74</v>
@@ -40914,7 +40918,7 @@
         <v>74</v>
       </c>
       <c r="AF372" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG372" t="s" s="2">
         <v>80</v>
@@ -40934,10 +40938,10 @@
     </row>
     <row r="373" hidden="true">
       <c r="A373" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C373" s="2"/>
       <c r="D373" t="s" s="2">
@@ -40964,12 +40968,12 @@
       </c>
       <c r="L373" s="2"/>
       <c r="M373" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N373" s="2"/>
       <c r="O373" s="2"/>
       <c r="P373" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q373" s="2"/>
       <c r="R373" t="s" s="2">
@@ -41015,7 +41019,7 @@
         <v>74</v>
       </c>
       <c r="AF373" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG373" t="s" s="2">
         <v>80</v>
@@ -41035,10 +41039,10 @@
     </row>
     <row r="374" hidden="true">
       <c r="A374" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C374" s="2"/>
       <c r="D374" t="s" s="2">
@@ -41114,7 +41118,7 @@
         <v>74</v>
       </c>
       <c r="AF374" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG374" t="s" s="2">
         <v>80</v>
@@ -41134,10 +41138,10 @@
     </row>
     <row r="375" hidden="true">
       <c r="A375" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C375" s="2"/>
       <c r="D375" t="s" s="2">
@@ -41160,7 +41164,7 @@
         <v>74</v>
       </c>
       <c r="K375" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L375" s="2"/>
       <c r="M375" s="2"/>
@@ -41213,7 +41217,7 @@
         <v>74</v>
       </c>
       <c r="AF375" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG375" t="s" s="2">
         <v>80</v>
@@ -41233,10 +41237,10 @@
     </row>
     <row r="376" hidden="true">
       <c r="A376" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C376" s="2"/>
       <c r="D376" t="s" s="2">
@@ -41259,7 +41263,7 @@
         <v>74</v>
       </c>
       <c r="K376" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L376" s="2"/>
       <c r="M376" s="2"/>
@@ -41312,7 +41316,7 @@
         <v>74</v>
       </c>
       <c r="AF376" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG376" t="s" s="2">
         <v>80</v>
@@ -41332,10 +41336,10 @@
     </row>
     <row r="377" hidden="true">
       <c r="A377" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C377" s="2"/>
       <c r="D377" t="s" s="2">
@@ -41358,13 +41362,13 @@
         <v>74</v>
       </c>
       <c r="K377" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="L377" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M377" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N377" s="2"/>
       <c r="O377" s="2"/>
@@ -41415,7 +41419,7 @@
         <v>74</v>
       </c>
       <c r="AF377" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG377" t="s" s="2">
         <v>80</v>
@@ -41435,10 +41439,10 @@
     </row>
     <row r="378" hidden="true">
       <c r="A378" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C378" s="2"/>
       <c r="D378" t="s" s="2">
@@ -41461,7 +41465,7 @@
         <v>74</v>
       </c>
       <c r="K378" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L378" s="2"/>
       <c r="M378" s="2"/>
@@ -41514,7 +41518,7 @@
         <v>74</v>
       </c>
       <c r="AF378" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG378" t="s" s="2">
         <v>80</v>
@@ -41534,10 +41538,10 @@
     </row>
     <row r="379" hidden="true">
       <c r="A379" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C379" s="2"/>
       <c r="D379" t="s" s="2">
@@ -41560,7 +41564,7 @@
         <v>74</v>
       </c>
       <c r="K379" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L379" s="2"/>
       <c r="M379" s="2"/>
@@ -41613,7 +41617,7 @@
         <v>74</v>
       </c>
       <c r="AF379" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG379" t="s" s="2">
         <v>80</v>
@@ -41633,10 +41637,10 @@
     </row>
     <row r="380" hidden="true">
       <c r="A380" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C380" s="2"/>
       <c r="D380" t="s" s="2">
@@ -41659,7 +41663,7 @@
         <v>74</v>
       </c>
       <c r="K380" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L380" s="2"/>
       <c r="M380" s="2"/>
@@ -41712,7 +41716,7 @@
         <v>74</v>
       </c>
       <c r="AF380" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG380" t="s" s="2">
         <v>80</v>
@@ -41732,10 +41736,10 @@
     </row>
     <row r="381" hidden="true">
       <c r="A381" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C381" s="2"/>
       <c r="D381" t="s" s="2">
@@ -41758,7 +41762,7 @@
         <v>74</v>
       </c>
       <c r="K381" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L381" s="2"/>
       <c r="M381" s="2"/>
@@ -41811,7 +41815,7 @@
         <v>74</v>
       </c>
       <c r="AF381" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG381" t="s" s="2">
         <v>80</v>
@@ -41831,10 +41835,10 @@
     </row>
     <row r="382" hidden="true">
       <c r="A382" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C382" s="2"/>
       <c r="D382" t="s" s="2">
@@ -41857,7 +41861,7 @@
         <v>74</v>
       </c>
       <c r="K382" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L382" s="2"/>
       <c r="M382" s="2"/>
@@ -41910,7 +41914,7 @@
         <v>74</v>
       </c>
       <c r="AF382" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG382" t="s" s="2">
         <v>80</v>
@@ -41930,10 +41934,10 @@
     </row>
     <row r="383" hidden="true">
       <c r="A383" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C383" s="2"/>
       <c r="D383" t="s" s="2">
@@ -41956,7 +41960,7 @@
         <v>74</v>
       </c>
       <c r="K383" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L383" s="2"/>
       <c r="M383" s="2"/>
@@ -42009,7 +42013,7 @@
         <v>74</v>
       </c>
       <c r="AF383" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG383" t="s" s="2">
         <v>80</v>
@@ -42029,10 +42033,10 @@
     </row>
     <row r="384" hidden="true">
       <c r="A384" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C384" s="2"/>
       <c r="D384" t="s" s="2">
@@ -42055,7 +42059,7 @@
         <v>74</v>
       </c>
       <c r="K384" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L384" s="2"/>
       <c r="M384" s="2"/>
@@ -42108,7 +42112,7 @@
         <v>74</v>
       </c>
       <c r="AF384" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG384" t="s" s="2">
         <v>80</v>
@@ -42128,10 +42132,10 @@
     </row>
     <row r="385" hidden="true">
       <c r="A385" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C385" s="2"/>
       <c r="D385" t="s" s="2">
@@ -42154,7 +42158,7 @@
         <v>74</v>
       </c>
       <c r="K385" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="L385" s="2"/>
       <c r="M385" s="2"/>
@@ -42207,7 +42211,7 @@
         <v>74</v>
       </c>
       <c r="AF385" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG385" t="s" s="2">
         <v>80</v>
@@ -42227,13 +42231,13 @@
     </row>
     <row r="386" hidden="true">
       <c r="A386" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D386" t="s" s="2">
         <v>74</v>
@@ -42255,7 +42259,7 @@
         <v>74</v>
       </c>
       <c r="K386" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L386" s="2"/>
       <c r="M386" s="2"/>
@@ -42308,7 +42312,7 @@
         <v>74</v>
       </c>
       <c r="AF386" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG386" t="s" s="2">
         <v>80</v>
@@ -42328,10 +42332,10 @@
     </row>
     <row r="387" hidden="true">
       <c r="A387" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C387" s="2"/>
       <c r="D387" t="s" s="2">
@@ -42429,10 +42433,10 @@
     </row>
     <row r="388" hidden="true">
       <c r="A388" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C388" s="2"/>
       <c r="D388" t="s" s="2">
@@ -42530,10 +42534,10 @@
     </row>
     <row r="389" hidden="true">
       <c r="A389" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C389" s="2"/>
       <c r="D389" t="s" s="2">
@@ -42631,10 +42635,10 @@
     </row>
     <row r="390" hidden="true">
       <c r="A390" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C390" s="2"/>
       <c r="D390" t="s" s="2">
@@ -42732,10 +42736,10 @@
     </row>
     <row r="391" hidden="true">
       <c r="A391" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C391" s="2"/>
       <c r="D391" t="s" s="2">
@@ -42835,10 +42839,10 @@
     </row>
     <row r="392" hidden="true">
       <c r="A392" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C392" s="2"/>
       <c r="D392" t="s" s="2">
@@ -42938,10 +42942,10 @@
     </row>
     <row r="393" hidden="true">
       <c r="A393" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C393" s="2"/>
       <c r="D393" t="s" s="2">
@@ -43041,10 +43045,10 @@
     </row>
     <row r="394" hidden="true">
       <c r="A394" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C394" s="2"/>
       <c r="D394" t="s" s="2">
@@ -43144,10 +43148,10 @@
     </row>
     <row r="395" hidden="true">
       <c r="A395" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C395" s="2"/>
       <c r="D395" t="s" s="2">
@@ -43245,10 +43249,10 @@
     </row>
     <row r="396" hidden="true">
       <c r="A396" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C396" s="2"/>
       <c r="D396" t="s" s="2">
@@ -43285,7 +43289,7 @@
         <v>74</v>
       </c>
       <c r="S396" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="T396" t="s" s="2">
         <v>74</v>
@@ -43304,7 +43308,7 @@
       </c>
       <c r="Y396" s="2"/>
       <c r="Z396" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AA396" t="s" s="2">
         <v>74</v>
@@ -43322,7 +43326,7 @@
         <v>74</v>
       </c>
       <c r="AF396" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG396" t="s" s="2">
         <v>75</v>
@@ -43342,10 +43346,10 @@
     </row>
     <row r="397" hidden="true">
       <c r="A397" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C397" s="2"/>
       <c r="D397" t="s" s="2">
@@ -43372,7 +43376,7 @@
       </c>
       <c r="L397" s="2"/>
       <c r="M397" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N397" s="2"/>
       <c r="O397" s="2"/>
@@ -43423,7 +43427,7 @@
         <v>74</v>
       </c>
       <c r="AF397" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG397" t="s" s="2">
         <v>80</v>
@@ -43443,10 +43447,10 @@
     </row>
     <row r="398" hidden="true">
       <c r="A398" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C398" s="2"/>
       <c r="D398" t="s" s="2">
@@ -43473,12 +43477,12 @@
       </c>
       <c r="L398" s="2"/>
       <c r="M398" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N398" s="2"/>
       <c r="O398" s="2"/>
       <c r="P398" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q398" s="2"/>
       <c r="R398" t="s" s="2">
@@ -43524,7 +43528,7 @@
         <v>74</v>
       </c>
       <c r="AF398" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG398" t="s" s="2">
         <v>80</v>
@@ -43544,10 +43548,10 @@
     </row>
     <row r="399" hidden="true">
       <c r="A399" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C399" s="2"/>
       <c r="D399" t="s" s="2">
@@ -43623,7 +43627,7 @@
         <v>74</v>
       </c>
       <c r="AF399" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG399" t="s" s="2">
         <v>80</v>
@@ -43643,10 +43647,10 @@
     </row>
     <row r="400" hidden="true">
       <c r="A400" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" t="s" s="2">
@@ -43669,7 +43673,7 @@
         <v>74</v>
       </c>
       <c r="K400" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L400" s="2"/>
       <c r="M400" s="2"/>
@@ -43722,7 +43726,7 @@
         <v>74</v>
       </c>
       <c r="AF400" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG400" t="s" s="2">
         <v>80</v>
@@ -43742,10 +43746,10 @@
     </row>
     <row r="401" hidden="true">
       <c r="A401" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C401" s="2"/>
       <c r="D401" t="s" s="2">
@@ -43768,7 +43772,7 @@
         <v>74</v>
       </c>
       <c r="K401" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L401" s="2"/>
       <c r="M401" s="2"/>
@@ -43821,7 +43825,7 @@
         <v>74</v>
       </c>
       <c r="AF401" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG401" t="s" s="2">
         <v>80</v>
@@ -43841,10 +43845,10 @@
     </row>
     <row r="402" hidden="true">
       <c r="A402" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C402" s="2"/>
       <c r="D402" t="s" s="2">
@@ -43867,13 +43871,13 @@
         <v>74</v>
       </c>
       <c r="K402" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="L402" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M402" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N402" s="2"/>
       <c r="O402" s="2"/>
@@ -43924,7 +43928,7 @@
         <v>74</v>
       </c>
       <c r="AF402" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG402" t="s" s="2">
         <v>80</v>
@@ -43944,10 +43948,10 @@
     </row>
     <row r="403" hidden="true">
       <c r="A403" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C403" s="2"/>
       <c r="D403" t="s" s="2">
@@ -43970,7 +43974,7 @@
         <v>74</v>
       </c>
       <c r="K403" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L403" s="2"/>
       <c r="M403" s="2"/>
@@ -44023,7 +44027,7 @@
         <v>74</v>
       </c>
       <c r="AF403" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG403" t="s" s="2">
         <v>80</v>
@@ -44043,10 +44047,10 @@
     </row>
     <row r="404" hidden="true">
       <c r="A404" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C404" s="2"/>
       <c r="D404" t="s" s="2">
@@ -44069,7 +44073,7 @@
         <v>74</v>
       </c>
       <c r="K404" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L404" s="2"/>
       <c r="M404" s="2"/>
@@ -44122,7 +44126,7 @@
         <v>74</v>
       </c>
       <c r="AF404" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG404" t="s" s="2">
         <v>80</v>
@@ -44142,10 +44146,10 @@
     </row>
     <row r="405" hidden="true">
       <c r="A405" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C405" s="2"/>
       <c r="D405" t="s" s="2">
@@ -44168,7 +44172,7 @@
         <v>74</v>
       </c>
       <c r="K405" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L405" s="2"/>
       <c r="M405" s="2"/>
@@ -44221,7 +44225,7 @@
         <v>74</v>
       </c>
       <c r="AF405" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG405" t="s" s="2">
         <v>80</v>
@@ -44241,10 +44245,10 @@
     </row>
     <row r="406" hidden="true">
       <c r="A406" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C406" s="2"/>
       <c r="D406" t="s" s="2">
@@ -44267,7 +44271,7 @@
         <v>74</v>
       </c>
       <c r="K406" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L406" s="2"/>
       <c r="M406" s="2"/>
@@ -44320,7 +44324,7 @@
         <v>74</v>
       </c>
       <c r="AF406" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG406" t="s" s="2">
         <v>80</v>
@@ -44340,10 +44344,10 @@
     </row>
     <row r="407" hidden="true">
       <c r="A407" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C407" s="2"/>
       <c r="D407" t="s" s="2">
@@ -44366,7 +44370,7 @@
         <v>74</v>
       </c>
       <c r="K407" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L407" s="2"/>
       <c r="M407" s="2"/>
@@ -44419,7 +44423,7 @@
         <v>74</v>
       </c>
       <c r="AF407" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG407" t="s" s="2">
         <v>80</v>
@@ -44439,10 +44443,10 @@
     </row>
     <row r="408" hidden="true">
       <c r="A408" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C408" s="2"/>
       <c r="D408" t="s" s="2">
@@ -44465,7 +44469,7 @@
         <v>74</v>
       </c>
       <c r="K408" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L408" s="2"/>
       <c r="M408" s="2"/>
@@ -44518,7 +44522,7 @@
         <v>74</v>
       </c>
       <c r="AF408" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG408" t="s" s="2">
         <v>80</v>
@@ -44538,10 +44542,10 @@
     </row>
     <row r="409" hidden="true">
       <c r="A409" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C409" s="2"/>
       <c r="D409" t="s" s="2">
@@ -44564,7 +44568,7 @@
         <v>74</v>
       </c>
       <c r="K409" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L409" s="2"/>
       <c r="M409" s="2"/>
@@ -44617,7 +44621,7 @@
         <v>74</v>
       </c>
       <c r="AF409" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG409" t="s" s="2">
         <v>80</v>
@@ -44637,10 +44641,10 @@
     </row>
     <row r="410" hidden="true">
       <c r="A410" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C410" s="2"/>
       <c r="D410" t="s" s="2">
@@ -44663,7 +44667,7 @@
         <v>74</v>
       </c>
       <c r="K410" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="L410" s="2"/>
       <c r="M410" s="2"/>
@@ -44716,7 +44720,7 @@
         <v>74</v>
       </c>
       <c r="AF410" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG410" t="s" s="2">
         <v>80</v>
@@ -44736,10 +44740,10 @@
     </row>
     <row r="411" hidden="true">
       <c r="A411" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C411" s="2"/>
       <c r="D411" t="s" s="2">
@@ -44762,7 +44766,7 @@
         <v>74</v>
       </c>
       <c r="K411" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="L411" s="2"/>
       <c r="M411" s="2"/>
@@ -44815,7 +44819,7 @@
         <v>74</v>
       </c>
       <c r="AF411" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AG411" t="s" s="2">
         <v>80</v>
@@ -44835,10 +44839,10 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C412" s="2"/>
       <c r="D412" t="s" s="2">
@@ -44861,13 +44865,13 @@
         <v>74</v>
       </c>
       <c r="K412" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="L412" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M412" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N412" s="2"/>
       <c r="O412" s="2"/>
@@ -44918,7 +44922,7 @@
         <v>74</v>
       </c>
       <c r="AF412" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AG412" t="s" s="2">
         <v>80</v>
@@ -44938,10 +44942,10 @@
     </row>
     <row r="413" hidden="true">
       <c r="A413" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C413" s="2"/>
       <c r="D413" t="s" s="2">
@@ -45039,10 +45043,10 @@
     </row>
     <row r="414" hidden="true">
       <c r="A414" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C414" s="2"/>
       <c r="D414" t="s" s="2">
@@ -45140,10 +45144,10 @@
     </row>
     <row r="415" hidden="true">
       <c r="A415" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C415" s="2"/>
       <c r="D415" t="s" s="2">
@@ -45241,10 +45245,10 @@
     </row>
     <row r="416" hidden="true">
       <c r="A416" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C416" s="2"/>
       <c r="D416" t="s" s="2">
@@ -45342,10 +45346,10 @@
     </row>
     <row r="417" hidden="true">
       <c r="A417" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C417" s="2"/>
       <c r="D417" t="s" s="2">
@@ -45445,10 +45449,10 @@
     </row>
     <row r="418" hidden="true">
       <c r="A418" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C418" s="2"/>
       <c r="D418" t="s" s="2">
@@ -45548,10 +45552,10 @@
     </row>
     <row r="419" hidden="true">
       <c r="A419" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C419" s="2"/>
       <c r="D419" t="s" s="2">
@@ -45651,10 +45655,10 @@
     </row>
     <row r="420" hidden="true">
       <c r="A420" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C420" s="2"/>
       <c r="D420" t="s" s="2">
@@ -45754,10 +45758,10 @@
     </row>
     <row r="421" hidden="true">
       <c r="A421" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C421" s="2"/>
       <c r="D421" t="s" s="2">
@@ -45855,10 +45859,10 @@
     </row>
     <row r="422" hidden="true">
       <c r="A422" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C422" s="2"/>
       <c r="D422" t="s" s="2">
@@ -45892,7 +45896,7 @@
       </c>
       <c r="Q422" s="2"/>
       <c r="R422" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="S422" t="s" s="2">
         <v>74</v>
@@ -45914,7 +45918,7 @@
       </c>
       <c r="Y422" s="2"/>
       <c r="Z422" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AA422" t="s" s="2">
         <v>74</v>
@@ -45932,7 +45936,7 @@
         <v>74</v>
       </c>
       <c r="AF422" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AG422" t="s" s="2">
         <v>80</v>
@@ -45952,10 +45956,10 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C423" s="2"/>
       <c r="D423" t="s" s="2">
@@ -45978,7 +45982,7 @@
         <v>74</v>
       </c>
       <c r="K423" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="L423" s="2"/>
       <c r="M423" s="2"/>
@@ -46031,7 +46035,7 @@
         <v>74</v>
       </c>
       <c r="AF423" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG423" t="s" s="2">
         <v>75</v>
@@ -46051,10 +46055,10 @@
     </row>
     <row r="424" hidden="true">
       <c r="A424" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C424" s="2"/>
       <c r="D424" t="s" s="2">
@@ -46152,10 +46156,10 @@
     </row>
     <row r="425" hidden="true">
       <c r="A425" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C425" s="2"/>
       <c r="D425" t="s" s="2">
@@ -46253,10 +46257,10 @@
     </row>
     <row r="426" hidden="true">
       <c r="A426" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C426" s="2"/>
       <c r="D426" t="s" s="2">
@@ -46354,10 +46358,10 @@
     </row>
     <row r="427" hidden="true">
       <c r="A427" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C427" s="2"/>
       <c r="D427" t="s" s="2">
@@ -46455,10 +46459,10 @@
     </row>
     <row r="428" hidden="true">
       <c r="A428" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C428" s="2"/>
       <c r="D428" t="s" s="2">
@@ -46558,10 +46562,10 @@
     </row>
     <row r="429" hidden="true">
       <c r="A429" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C429" s="2"/>
       <c r="D429" t="s" s="2">
@@ -46661,10 +46665,10 @@
     </row>
     <row r="430" hidden="true">
       <c r="A430" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C430" s="2"/>
       <c r="D430" t="s" s="2">
@@ -46764,10 +46768,10 @@
     </row>
     <row r="431" hidden="true">
       <c r="A431" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C431" s="2"/>
       <c r="D431" t="s" s="2">
@@ -46867,10 +46871,10 @@
     </row>
     <row r="432" hidden="true">
       <c r="A432" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C432" s="2"/>
       <c r="D432" t="s" s="2">
@@ -46968,10 +46972,10 @@
     </row>
     <row r="433" hidden="true">
       <c r="A433" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C433" s="2"/>
       <c r="D433" t="s" s="2">
@@ -47001,7 +47005,7 @@
       <c r="N433" s="2"/>
       <c r="O433" s="2"/>
       <c r="P433" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="Q433" s="2"/>
       <c r="R433" t="s" s="2">
@@ -47027,7 +47031,7 @@
       </c>
       <c r="Y433" s="2"/>
       <c r="Z433" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AA433" t="s" s="2">
         <v>74</v>
@@ -47045,7 +47049,7 @@
         <v>74</v>
       </c>
       <c r="AF433" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AG433" t="s" s="2">
         <v>80</v>
@@ -47065,10 +47069,10 @@
     </row>
     <row r="434" hidden="true">
       <c r="A434" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C434" s="2"/>
       <c r="D434" t="s" s="2">
@@ -47102,7 +47106,7 @@
       </c>
       <c r="Q434" s="2"/>
       <c r="R434" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="S434" t="s" s="2">
         <v>74</v>
@@ -47124,7 +47128,7 @@
       </c>
       <c r="Y434" s="2"/>
       <c r="Z434" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AA434" t="s" s="2">
         <v>74</v>
@@ -47142,7 +47146,7 @@
         <v>74</v>
       </c>
       <c r="AF434" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AG434" t="s" s="2">
         <v>80</v>
@@ -47162,10 +47166,10 @@
     </row>
     <row r="435" hidden="true">
       <c r="A435" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C435" s="2"/>
       <c r="D435" t="s" s="2">
@@ -47221,7 +47225,7 @@
       </c>
       <c r="Y435" s="2"/>
       <c r="Z435" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AA435" t="s" s="2">
         <v>74</v>
@@ -47239,7 +47243,7 @@
         <v>74</v>
       </c>
       <c r="AF435" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG435" t="s" s="2">
         <v>80</v>
@@ -47259,10 +47263,10 @@
     </row>
     <row r="436" hidden="true">
       <c r="A436" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C436" s="2"/>
       <c r="D436" t="s" s="2">
@@ -47338,7 +47342,7 @@
         <v>74</v>
       </c>
       <c r="AF436" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG436" t="s" s="2">
         <v>80</v>
@@ -47358,10 +47362,10 @@
     </row>
     <row r="437" hidden="true">
       <c r="A437" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C437" s="2"/>
       <c r="D437" t="s" s="2">
@@ -47384,7 +47388,7 @@
         <v>74</v>
       </c>
       <c r="K437" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="L437" s="2"/>
       <c r="M437" s="2"/>
@@ -47437,7 +47441,7 @@
         <v>74</v>
       </c>
       <c r="AF437" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AG437" t="s" s="2">
         <v>80</v>
@@ -47457,10 +47461,10 @@
     </row>
     <row r="438" hidden="true">
       <c r="A438" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C438" s="2"/>
       <c r="D438" t="s" s="2">
@@ -47483,7 +47487,7 @@
         <v>74</v>
       </c>
       <c r="K438" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L438" s="2"/>
       <c r="M438" s="2"/>
@@ -47536,7 +47540,7 @@
         <v>74</v>
       </c>
       <c r="AF438" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AG438" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
